--- a/louvers/files/reference_xls/price_xls/cottal_85.xlsx
+++ b/louvers/files/reference_xls/price_xls/cottal_85.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A6E45D-0F8F-A640-9560-E3816D0061CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8323B648-4F43-4F4A-B70B-7F1D8DC8D1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17660" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
   <sheets>
     <sheet name="Price" sheetId="1" r:id="rId1"/>
@@ -964,36 +964,30 @@
         <v>8</v>
       </c>
       <c r="B2" s="18">
-        <f>CEILING(1.27*650, 10)</f>
-        <v>830</v>
+        <v>913.00000000000011</v>
       </c>
       <c r="C2" s="19">
-        <f>CEILING(1.27*6917, 10)</f>
-        <v>8790</v>
+        <v>9669</v>
       </c>
       <c r="D2" s="20">
         <f>CEILING(1.27*623, 10)</f>
         <v>800</v>
       </c>
       <c r="E2" s="21">
-        <f>CEILING(1.27*750, 10)</f>
-        <v>960</v>
+        <v>1056</v>
       </c>
       <c r="F2" s="22">
-        <f>CEILING(1.27*8002, 10)</f>
-        <v>10170</v>
+        <v>11187</v>
       </c>
       <c r="G2" s="23">
         <f>CEILING(1.27*692, 10)</f>
         <v>880</v>
       </c>
       <c r="H2" s="24">
-        <f>CEILING(1.27*830, 10)</f>
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="I2" s="25">
-        <f>CEILING(1.27*8870, 10)</f>
-        <v>11270</v>
+        <v>12397.000000000002</v>
       </c>
       <c r="J2" s="26">
         <f>CEILING(1.27*790, 10)</f>
@@ -1005,30 +999,24 @@
         <v>9</v>
       </c>
       <c r="B3" s="9">
-        <f>B2</f>
-        <v>830</v>
+        <v>913.00000000000011</v>
       </c>
       <c r="C3" s="9">
-        <f>C2</f>
-        <v>8790</v>
+        <v>9669</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="15">
-        <f>E2</f>
-        <v>960</v>
+        <v>1056</v>
       </c>
       <c r="F3" s="11">
-        <f>F2</f>
-        <v>10170</v>
+        <v>11187</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="12">
-        <f>H2</f>
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="I3" s="13">
-        <f>I2</f>
-        <v>11270</v>
+        <v>12397.000000000002</v>
       </c>
       <c r="J3" s="14"/>
     </row>
